--- a/Employee_Reports_wi48/Emmanuel Richard Marasigan Velasco Q0615.xlsx
+++ b/Employee_Reports_wi48/Emmanuel Richard Marasigan Velasco Q0615.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Tilting deck (Cargo Trainings)</t>
+          <t>Weight scales (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-009</t>
+          <t>LSME-CRG-M-013</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -805,20 +805,20 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>21-Oct-2025</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>21-Oct-2027</t>
+          <t>08-Apr-2028</t>
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>465</v>
+        <v>632</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>TT+RA (Cargo Trainings)</t>
+          <t>Tilting deck (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-007</t>
+          <t>LSME-CRG-M-009</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -854,20 +854,20 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>22-Oct-2025</t>
+          <t>21-Oct-2025</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>22-Oct-2027</t>
+          <t>21-Oct-2027</t>
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>CS-Hoist (Cargo Trainings)</t>
+          <t>TT+RA (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-001</t>
+          <t>LSME-CRG-M-007</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -903,20 +903,20 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>21-Oct-2025</t>
+          <t>22-Oct-2025</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>21-Oct-2027</t>
+          <t>22-Oct-2027</t>
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>ULD Hoist (Cargo Trainings)</t>
+          <t>CS-Hoist (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-008</t>
+          <t>LSME-CRG-M-001</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -952,20 +952,20 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>22-Oct-2025</t>
+          <t>21-Oct-2025</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>22-Oct-2027</t>
+          <t>21-Oct-2027</t>
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Truck dock (Cargo Trainings)</t>
+          <t>ULD Hoist (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-006</t>
+          <t>LSME-CRG-M-008</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1001,20 +1001,20 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>22-Oct-2025</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2027</t>
+          <t>22-Oct-2027</t>
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Control circuits (Cargo Trainings)</t>
+          <t>Truck dock (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-019</t>
+          <t>LSME-CRG-M-006</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1050,20 +1050,20 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>19-Feb-2028</t>
+          <t>11-Jul-2028</t>
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>586</v>
+        <v>726</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Cool Room (Cargo Trainings)</t>
+          <t>Truck dock 20FT (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-011</t>
+          <t>LSME-CRG-M-020</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1099,20 +1099,20 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>12-Jul-2026</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2027</t>
+          <t>11-Jul-2028</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>469</v>
+        <v>726</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Climate Control Center (Cargo Trainings)</t>
+          <t>Control circuits (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-014</t>
+          <t>LSME-CRG-M-019</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1148,20 +1148,20 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>19-Feb-2026</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2027</t>
+          <t>19-Feb-2028</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>469</v>
+        <v>583</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1177,28 +1177,40 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Powered roller Decks2 (Cargo Trainings)</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr"/>
-      <c r="D16" s="3" t="inlineStr"/>
-      <c r="E16" s="3" t="inlineStr"/>
+          <t>Cool Room (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-011</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>18-Feb-2026</t>
+          <t>25-Oct-2025</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>18-Feb-2028</t>
+          <t>25-Oct-2027</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>585</v>
+        <v>466</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1214,40 +1226,40 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Lodige LOTO Procedure (SOPs)</t>
+          <t>Climate Control Center (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>ELECTRICAL SAFETY</t>
+          <t>CARGO</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>LSME-OHS-SOP-021</t>
+          <t>LSME-CRG-M-014</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>SOP</t>
+          <t>EQUIPMENT MANUAL</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>20-Oct-2025</t>
+          <t>25-Oct-2025</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>20-Oct-2026</t>
+          <t>25-Oct-2027</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>99</v>
+        <v>466</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1263,41 +1275,28 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Equipment Operation Procedure
-(SOP-031) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>CARGO</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
-        <is>
-          <t>LSME-CRG-SOP-031</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
+          <t>Powered roller Decks2 (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr"/>
+      <c r="E18" s="3" t="inlineStr"/>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>18-Feb-2026</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2026</t>
+          <t>18-Feb-2028</t>
         </is>
       </c>
       <c r="H18" s="3" t="n">
-        <v>104</v>
+        <v>582</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -1313,17 +1312,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
+          <t>Lodige LOTO Procedure (SOPs)</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>CARGO</t>
+          <t>ELECTRICAL SAFETY</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-028</t>
+          <t>LSME-OHS-SOP-021</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -1333,20 +1332,20 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>20-Oct-2025</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2026</t>
+          <t>20-Oct-2026</t>
         </is>
       </c>
       <c r="H19" s="3" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -1362,7 +1361,8 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Misaligned Pallet-ULD Recovery Procedure (SOPs)</t>
+          <t>Equipment Operation Procedure
+(SOP-031) (SOPs)</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-030</t>
+          <t>LSME-CRG-SOP-031</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -1382,20 +1382,20 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>14-Jan-2026</t>
+          <t>25-Oct-2025</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>14-Jan-2027</t>
+          <t>25-Oct-2026</t>
         </is>
       </c>
       <c r="H20" s="3" t="n">
-        <v>185</v>
+        <v>101</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
+          <t>Equipment  Request &amp;handover procedure(SOP-028) (SOPs)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-SOP-041</t>
+          <t>LSME-CRG-SOP-028</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -1431,20 +1431,20 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2026</t>
+          <t>25-Oct-2025</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>23-Apr-2027</t>
+          <t>25-Oct-2026</t>
         </is>
       </c>
       <c r="H21" s="3" t="n">
-        <v>284</v>
+        <v>101</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -1460,28 +1460,40 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C22" s="3" t="inlineStr"/>
-      <c r="D22" s="3" t="inlineStr"/>
-      <c r="E22" s="3" t="inlineStr"/>
+          <t>Misaligned Pallet-ULD Recovery Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-030</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>14-Jan-2026</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2026</t>
+          <t>14-Jan-2027</t>
         </is>
       </c>
       <c r="H22" s="3" t="n">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -1497,28 +1509,40 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C23" s="3" t="inlineStr"/>
-      <c r="D23" s="3" t="inlineStr"/>
-      <c r="E23" s="3" t="inlineStr"/>
+          <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-SOP-041</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2025</t>
+          <t>23-Apr-2026</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>25-Oct-2026</t>
+          <t>23-Apr-2027</t>
         </is>
       </c>
       <c r="H23" s="3" t="n">
-        <v>104</v>
+        <v>281</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -1534,7 +1558,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>EOP For ULD System Failure (SOPs)</t>
+          <t>POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr"/>
@@ -1551,11 +1575,11 @@
         </is>
       </c>
       <c r="H24" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -1571,7 +1595,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>EOP For CS System Failure (SOPs)</t>
+          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr"/>
@@ -1588,11 +1612,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -1608,7 +1632,7 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>20FT Floor Scale Weight Discrepancy Troubleshooting Guide (SOPs)</t>
+          <t>EOP For ULD System Failure (SOPs)</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr"/>
@@ -1616,20 +1640,20 @@
       <c r="E26" s="3" t="inlineStr"/>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>29-Jan-2026</t>
+          <t>25-Oct-2025</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>29-Jan-2027</t>
+          <t>25-Oct-2026</t>
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>200</v>
+        <v>101</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -1645,7 +1669,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>PM Of CS H9 TV (SOPs)</t>
+          <t>EOP For CS System Failure (SOPs)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr"/>
@@ -1653,28 +1677,102 @@
       <c r="E27" s="3" t="inlineStr"/>
       <c r="F27" s="3" t="inlineStr">
         <is>
+          <t>25-Oct-2025</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>25-Oct-2026</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>101</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>20FT Floor Scale Weight Discrepancy Troubleshooting Guide (SOPs)</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr"/>
+      <c r="D28" s="3" t="inlineStr"/>
+      <c r="E28" s="3" t="inlineStr"/>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>29-Jan-2026</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>29-Jan-2027</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>197</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>PM Of CS H9 TV (SOPs)</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr"/>
+      <c r="D29" s="3" t="inlineStr"/>
+      <c r="E29" s="3" t="inlineStr"/>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
           <t>11-Jun-2026</t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G29" s="3" t="inlineStr">
         <is>
           <t>11-Jun-2027</t>
         </is>
       </c>
-      <c r="H27" s="3" t="n">
-        <v>333</v>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr"/>
+      <c r="H29" s="3" t="n">
+        <v>330</v>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2066,7 +2164,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -2095,7 +2193,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -2124,7 +2222,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -2153,7 +2251,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -2182,7 +2280,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7949</v>
+        <v>7946</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -2211,7 +2309,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -2240,7 +2338,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -2269,7 +2367,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -2298,7 +2396,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -2327,7 +2425,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -2356,7 +2454,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -2385,7 +2483,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -2414,7 +2512,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -2443,7 +2541,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -2472,7 +2570,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7948</v>
+        <v>7945</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -2501,7 +2599,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -2530,7 +2628,7 @@
         </is>
       </c>
       <c r="E19" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -2559,7 +2657,7 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
@@ -2588,7 +2686,7 @@
         </is>
       </c>
       <c r="E21" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
@@ -2617,7 +2715,7 @@
         </is>
       </c>
       <c r="E22" s="3" t="n">
-        <v>7948</v>
+        <v>7945</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -2646,7 +2744,7 @@
         </is>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7953</v>
+        <v>7950</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
